--- a/templates/insurance/公积金分单位模板.xlsx
+++ b/templates/insurance/公积金分单位模板.xlsx
@@ -443,20 +443,20 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr">
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
         <is>
           <t>补收</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
         <is>
           <t>转款金额</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
@@ -567,16 +567,8 @@
           <t>1776.00</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>2960.00</t>
@@ -585,11 +577,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>2960.00</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>1184.00</t>
@@ -600,16 +588,8 @@
           <t>1776.00</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr">
         <is>
           <t>2960.00</t>
@@ -653,26 +633,10 @@
           <t>2960.00</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>1184.00</t>

--- a/templates/insurance/公积金分单位模板.xlsx
+++ b/templates/insurance/公积金分单位模板.xlsx
@@ -439,28 +439,16 @@
           <t>已参保</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>补收</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>转款金额</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr"/>
@@ -695,6 +683,11 @@
       </c>
     </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="M2:Q2"/>
+    <mergeCell ref="C2:H2"/>
+    <mergeCell ref="I2:L2"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>